--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -697,7 +697,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>16 filas de datos</t>
+          <t>20 filas de datos</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -848,28 +848,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Eliava (14/14 menciones); Intesti (13/19 menciones)</t>
-        </is>
-      </c>
+          <t>firme: A declara casos ya publicados y cita a B</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>título (2 de 5 trozos)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>multicentrico (europa)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -879,30 +879,34 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -912,18 +916,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>firme: A declara casos ya publicados y cita a B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>título (3 de 5 trozos)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Intesti (13/7 menciones)</t>
+          <t>Intesti (3/7 menciones)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>multicentrico (europa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -933,7 +941,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,7 +951,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -951,43 +959,51 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>firme: A declara casos ya publicados y cita a B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>título (4 de 6 trozos)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eliava (14/15 menciones); Intesti (13/12 menciones); Pyo bacteriophage (4/12 menciones)</t>
+          <t>BFC-1 (7/12 menciones)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>multicentrico (europa)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>belgica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -997,79 +1013,87 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Eliava (14/5 menciones); Pyo bacteriophage (4/30 menciones)</t>
-        </is>
-      </c>
+          <t>firme: A declara casos ya publicados y cita a B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>título (5 de 6 trozos)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>multicentrico (europa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>letonia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-009</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EST-015</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1080,7 +1104,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PASA16 (51/6 menciones)</t>
+          <t>Eliava (14/14 menciones); Intesti (13/19 menciones)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1100,17 +1124,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1118,37 +1142,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EST-016</t>
+          <t>EST-009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>identificador 10.3390/v11100891</t>
-        </is>
-      </c>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BFC-1 (26/12 menciones)</t>
+          <t>Intesti (13/7 menciones)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>letonia</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>belgica</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1158,34 +1178,30 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>gyofosteomyelitis:apopulation- (2019)11:891.doi:10.3390/v11100891 based study, 1969 to 2009. J Bone Joint Surg Am. (2015) 97:837– 10. TkhilaishviliT,WinklerT,MüllerM,PerkaC,TrampuzA.Bacteriophages 4</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-009</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1196,7 +1212,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Intesti (19/7 menciones)</t>
+          <t>Eliava (14/15 menciones); Intesti (13/12 menciones); Pyo bacteriophage (4/12 menciones)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1211,7 +1227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1226,7 +1242,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1234,12 +1250,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1250,7 +1266,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eliava (14/15 menciones); Intesti (19/12 menciones)</t>
+          <t>Eliava (14/5 menciones); Pyo bacteriophage (4/30 menciones)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1265,12 +1281,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1280,7 +1296,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1288,12 +1304,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-015</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1304,7 +1320,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eliava (14/5 menciones)</t>
+          <t>PASA16 (51/6 menciones)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1319,22 +1335,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1342,33 +1358,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-016</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>a comprobar: cita + mismo producto</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>identificador 10.3390/v11100891</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intesti (7/12 menciones)</t>
+          <t>BFC-1 (26/12 menciones)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>letonia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>belgica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1378,30 +1398,34 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>gyofosteomyelitis:apopulation- (2019)11:891.doi:10.3390/v11100891 based study, 1969 to 2009. J Bone Joint Surg Am. (2015) 97:837– 10. TkhilaishviliT,WinklerT,MüllerM,PerkaC,TrampuzA.Bacteriophages 4</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1436,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AB-PA01 (54/49 menciones)</t>
+          <t>Intesti (19/7 menciones)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1427,22 +1451,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1450,74 +1474,66 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>identificador 10.1038/s41564-024-01705-x</t>
-        </is>
-      </c>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eliava (4/10 menciones); Intesti (19/3 menciones)</t>
+          <t>Eliava (14/15 menciones); Intesti (19/12 menciones)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>alemania</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>multicentrico (europa)</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>, Geissberger F-D, Kufner V, Schmutz S, Böni J, et al. s41564-024-01705-x Optimization and validation of sample preparation for metagenomic sequencing of 7. Briot T, Kolenda C, Ferry T, Medina M, Laurent F, L</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1528,37 +1544,37 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC-1 (12/12 menciones)</t>
+          <t>Eliava (14/5 menciones)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>belgica</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>belgica</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1566,74 +1582,66 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EST-003</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>identificador 10.1016/j.medj.2023.07.002</t>
-        </is>
-      </c>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PASA16 (23/51 menciones)</t>
+          <t>Intesti (7/12 menciones)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>multicentrico (internacional)</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>israel</t>
+          <t>eeuu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>rapy related microbial succession associated j.medj.2023.07.002 with successful clinical outcome for a recurrent urinary tract infection. 20. Hope KD, Tunuguntla HP, Puri K, Spinner JA, Choudhry S,</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1644,43 +1652,275 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
+          <t>AB-PA01 (54/49 menciones)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>eeuu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>eeuu</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EST-051</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EST-108</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>a comprobar: cita + mismo producto</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>identificador 10.1038/s41564-024-01705-x</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Eliava (4/10 menciones); Intesti (19/3 menciones)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>alemania</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>multicentrico (europa)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>, Geissberger F-D, Kufner V, Schmutz S, Böni J, et al. s41564-024-01705-x Optimization and validation of sample preparation for metagenomic sequencing of 7. Briot T, Kolenda C, Ferry T, Medina M, Laurent F, L</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EST-062</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EST-164</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BFC-1 (12/12 menciones)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>belgica</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>belgica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EST-077</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EST-003</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>a comprobar: cita + mismo producto</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>identificador 10.1016/j.medj.2023.07.002</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PASA16 (23/51 menciones)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>multicentrico (internacional)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>rapy related microbial succession associated j.medj.2023.07.002 with successful clinical outcome for a recurrent urinary tract infection. 20. Hope KD, Tunuguntla HP, Puri K, Spinner JA, Choudhry S,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EST-080</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EST-134</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Eliava (15/5 menciones); Pyo bacteriophage (12/30 menciones)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>eeuu</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>eeuu</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>eeuu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>eeuu</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L17"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -697,7 +697,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>Cada par de estudios que podía describir a los mismos pacientes, con el veredicto tras leer los dos artículos y los pacientes que comparten, una clave por persona.</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sección 4.4, limitación séptima. Un paciente que sale en tres pares tiene la misma clave en los tres y se cuenta una vez.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -529,7 +533,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20 filas de datos</t>
+          <t>31 filas de datos</t>
         </is>
       </c>
     </row>
@@ -546,144 +550,144 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>estudio_a</t>
+          <t>estudio_1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>columna interna: estudio_a</t>
+          <t>columna interna: estudio_1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>estudio_b</t>
+          <t>estudio_2</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>columna interna: estudio_b</t>
+          <t>columna interna: estudio_2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>fuerza</t>
+          <t>clave_del_paciente</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>columna interna: fuerza</t>
+          <t>columna interna: clave_del_paciente</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>como_lo_nombra</t>
+          <t>pacientes_de_esa_clave</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>columna interna: como_lo_nombra</t>
+          <t>columna interna: pacientes_de_esa_clave</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>producto_comun</t>
+          <t>paciente_o_identificador</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>columna interna: producto_comun</t>
+          <t>columna interna: paciente_o_identificador</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>pais_a</t>
+          <t>senal_que_lo_marco</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>columna interna: pais_a</t>
+          <t>columna interna: senal_que_lo_marco</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>pais_b</t>
+          <t>Evidencia</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>columna interna: pais_b</t>
+          <t>columna interna: evidencia</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>pacientes_a</t>
+          <t>pacientes_potencialmente_duplicados</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>columna interna: pacientes_a</t>
+          <t>columna interna: pacientes_potencialmente_duplicados</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>pacientes_b</t>
+          <t>brazos_afectados</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>columna interna: pacientes_b</t>
+          <t>columna interna: brazos_afectados</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>anio_a</t>
+          <t>se_conto_una_o_dos_veces</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>columna interna: anio_a</t>
+          <t>columna interna: se_conto_una_o_dos_veces</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>anio_b</t>
+          <t>veredicto</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>columna interna: anio_b</t>
+          <t>columna interna: veredicto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>fragmento</t>
+          <t>accion_necesaria</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>columna interna: fragmento</t>
+          <t>columna interna: accion_necesaria</t>
         </is>
       </c>
     </row>
@@ -697,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -712,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -721,7 +725,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -732,443 +736,471 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>estudio_a</t>
+          <t>estudio_1</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>estudio_b</t>
+          <t>estudio_2</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>fuerza</t>
+          <t>clave_del_paciente</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>como_lo_nombra</t>
+          <t>pacientes_de_esa_clave</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>producto_comun</t>
+          <t>paciente_o_identificador</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>pais_a</t>
+          <t>senal_que_lo_marco</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>pais_b</t>
+          <t>Evidencia</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>pacientes_a</t>
+          <t>pacientes_potencialmente_duplicados</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>pacientes_b</t>
+          <t>brazos_afectados</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>anio_a</t>
+          <t>se_conto_una_o_dos_veces</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>anio_b</t>
+          <t>veredicto</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>fragmento</t>
+          <t>accion_necesaria</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EST-026</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>firme: cita + marca de publicación previa</t>
+          <t>P20 infección de injerto vascular (Blasco 2023)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>identificador NCT05269134</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1 (por cita; número de paciente en EST-108 no identificable)</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>eeuu</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>NO lo marco el detector: lo encontro la lectura del 2026-09-30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Solapan (por cita): EST-108 incluye entre sus 27 casos ya publicados el de la ref. 26 (Blasco 2023), que es EST-002 (infección de injerto vascular, fagos de QAMH en julio de 2021, dentro de la ventana de EST-108). El número de paciente no se puede identificar porque su tabla no lo incluye y la Supplementary Table 1 no viene en el PDF. — EST-108: «Twenty-seven of the 100 BT cases/patients were previously reported» (p. 2) | EST-108: «26. Blasco, L. et al. Case report: analysis of phage therapy failure in a patient with a Pseudomonas aeruginosa prosthetic vascular graft infection» (p. 17) | EST-002: «In July 2021, 70 ml of the bacteriophage cocktail, consisting of the three phages» (p. 2) | EST-002: «therapeutic phages were obtained from the Queen Astrid Military Hospital (Brussels, Belgium)» (p. 2)</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 (por cita)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>EST-002: A | EST-108: A,B,C,D</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">an overall decrease in inflammatory markers (Fig. 2c, Supplementary Table 4). No significant adverse events were observed while on phage therapy. There was a transient elevation in liver enzymes which other groups have previously reported12 (Fig. 2d). The patient has remained off antibiotics and has remained asymptomatic at 2-year follow-up with baseline ambulatory function comparable to prior to </t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EST-034</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>firme: A declara casos ya publicados y cita a B</t>
+          <t>P1 niña de 10 años, Berlin Heart EXCOR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>título (2 de 5 trozos)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1 (EST-077 caso 3 = EST-003 caso 3)</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>multicentrico (europa)</t>
+          <t>a comprobar: cita + mismo producto</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el caso 3 de EST-077 (niña de 10 años con Berlin Heart Excor, bacteriemia por P. aeruginosa, PASA16 + meropenem) es el caso 3 de EST-003 (10/F, Berlin heart EXCOR, meropenem, fallecida). — EST-077: «A 10-year-old female with a genetic cardiomyopathy was admitted with cardiogenic shock and underwent placement of a Berlin Heart Excor VAD in January 2019 as a bridge to transplant.» (p. 11) | EST-077: «was started on IV monophage PASA16» (p. 11) | EST-003: «3 bacteremia 10/F prosthetic device infection (Berlin heart EXCOR) MDR i.v., 49 days BID» (p. 7)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>EST-003: A,B,C,D,E | EST-077: A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>firme: A declara casos ya publicados y cita a B</t>
+          <t>P2 niña de 7 años, infección osteoarticular</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>título (3 de 5 trozos)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Intesti (3/7 menciones)</t>
+          <t>1 (EST-003 caso 4 = paciente de EST-095)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>multicentrico (europa)</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: EST-095 (Khatami et al., niña de 7 años con osteoartritis crónica por P. aeruginosa, PASA16 i.v. con colistina y aztreonam) es el caso 4 de EST-003, que lo identifica como caso publicado por «Khatami et al.». — EST-003: «4 osteomyelitis 7/F surgical debridement XDR i.v., 14 days» (p. 7) | EST-003: «8 months Khatami et al» (p. 7) | EST-095: «complicating the internal fixation of a traumatic fracture-dislocation in a 7-yearold girl» (p. 1) | EST-095: «beginning three months into a twelvemonth course of IV colistin and aztreonam» (p. 1)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-003: A,B,C,D,E | EST-095: A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-015</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>firme: A declara casos ya publicados y cita a B</t>
+          <t>P3 varón de 25 años, osteomielitis craneal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>título (4 de 6 trozos)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC-1 (7/12 menciones)</t>
+          <t>1 (EST-003 caso 9 = paciente de EST-015)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>multicentrico (europa)</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>belgica</t>
+          <t>Solapan: el caso 9 de EST-003 (varón de 25 años, osteomielitis craneal, PASA16 + cefiderocol) es el paciente de EST-015; EST-003 lo identifica como caso publicado por «Simner et al.». — EST-003: «9 osteomyelitis 25/M debrided cranial bone and scalp tissue XDR i.v., 30 days BID» (p. 7) | EST-003: «Simner, P.J., Cherian, J., Suh, G.A., Bergman, Y., Beisken, S., Fackler, J., Lee, M., Hopkins, R.J., and Tamma, P.D. (2022). Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyelitis» (p. 13) | EST-015: «We report the case of a 25-year-old male who experienced an accidental electrocution resulting in exposed calvarium in the left parieto-temporal region» (p. 1)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-003: A,B,C,D,E | EST-015: A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-012</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>firme: A declara casos ya publicados y cita a B</t>
+          <t>P4 varón de 96 años, infección protésica</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>título (5 de 6 trozos)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1 (EST-003 caso 10 = paciente de EST-012)</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>multicentrico (europa)</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>letonia</t>
+          <t>Solapan: el caso 10 de EST-003 (varón de 96 años, infección protésica, PASA16 + PaWRA02Phi83) es el paciente de EST-012; ambos artículos dan la misma aprobación de emergencia de UPMC (EA21110067). — EST-003: «10 prosthetic joint infection 96/M synovial fluid tissue sonicate S» (p. 7) | EST-003: «UPMC emergency approval number EA21110067» (p. 15) | EST-012: «A 96-year-old male with multiple comorbidities including heart failure presented with a chronic multidrug-resistant Pseudomonas aeruginosa infection in complex implants.» (p. 5) | EST-012: «We obtained compassionateuse IRB (EA21110067) from the University of Pittsburgh» (p. 13)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-003: A,B,C,D,E | EST-012: A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Belgian BT consortium, consisting of the Queen Astrid Military Hospi- pitals, 29 cities and 12 countries (Fig. 1a). Twenty-seven of the 100 BT tal (QAMH), KU Leuven and Sciensano (formerly known as the Scientific cases/patients were previously reported6,13–26. Since 2008, the number Institute of Public Health), facilitated BT in about 140 difficult-to-treat of BT cases performed under the umbrella</t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>P12 varón de 46 años, osteomielitis; P2 niña de 7 años, infección osteoarticular; P1 niña de 10 años, Berlin Heart EXCOR; P13 varón de 69 años, mastoiditis; P14 mujer de 41 años, infección por silicona; P15 varón de 32 años, infección ósea</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eliava (14/14 menciones); Intesti (13/19 menciones)</t>
+          <t>6 (casos 1, 2, 3, 4, 7 y 10 de EST-070 = casos 1, 4, 3, 5, 7 y 8 de EST-003)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: son dos series del mismo centro (IPTC, Nir-Paz/Onallah). Los 6 casos de P. aeruginosa tratados con PASA16 en EST-070 coinciden en edad, sexo, indicación y antibiótico con casos de EST-003: 46/M osteomielitis + ceftazidima; 7/F osteomielitis XDR; 10/F Berlin Heart + meropenem; 69/M mastoiditis + ceftazidima; 41/F infección por silicona PDR + meropenem; 32/M infección ósea + ceftazidima-avibactam. — EST-070: «1 46 M Pseudomonas aeruginosa (MDR) Osteomyelitis Pa14NøPASA16 (APT) Ceftazidime Remission» (p. 6) | EST-070: «2 7 F P aeruginosa (XDR) Osteomyelitis Pa14NøPASA16 (APT)» (p. 6) | EST-070: «3 10 F P aeruginosa (MDR) Berlin heart intravascular infection Pa14NøPASA16 (APT) Meropenem» (p. 6) | EST-070: «4 69 M P aeruginosa (susceptible) Mastoiditis + osteomyelitis» (p. 6) | EST-070: «7 41 F P aeruginosa (PDR) Infected silicone injection» (p. 6) | EST-070: «10 32 M P aeruginosa (MDR) Bone infection Pa14NøPASA16 (APT) Ceftazidime-avibactam, ciprofloxacin» (p. 6) | EST-003: «1 osteomyelitis 46/M wound tibial infection MDR i.v., 14 days BID» (p. 7) | EST-003: «3 bacteremia 10/F prosthetic device infection (Berlin heart EXCOR) MDR i.v., 49 days BID» (p. 7) | EST-003: «4 osteomyelitis 7/F surgical debridement XDR» (p. 7) | EST-003: «5 mastoiditis 69/M ear infection S i.v., 14 days BID» (p. 7) | EST-003: «7 skin and soft tissue infection 41/F massive silicon soft tissue infection» (p. 7) | EST-003: «8 osteomyelitis 32/M surgery wound MDR intraoperative + i.v., 28 days BID» (p. 7)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>EST-003: A,B,C,D,E | EST-070: A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>P5 infección espinal panresistente</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Intesti (13/7 menciones)</t>
+          <t>1 (EST-108 paciente 26 = paciente de EST-010)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el paciente 26 de EST-108 (infección espinal por P. aeruginosa, fagos 4029, 4032 y 4034, vía local e i.v.) es el paciente de EST-010; EST-108 lo cita como ref. 20 (Ferry 2022). — EST-108: «26 Spinal infection P. aeruginosa 4029, 4032 and 4034 Local and intravenous» (p. 5) | EST-108: «20. Ferry, T. et al. Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection» (p. 17) | EST-010: «A 74-year-old man with melanoma treated with anti-PD1 (pembrolizumab) experienced a catheter-related bacteremia» (p. 2) | EST-010: «three active phages (named vB_PaeP_4029, vB_PaeP_4032 and vB_PaeP_4034)» (p. 5)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1178,51 +1210,59 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-010: A | EST-108: A,B,C,D</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-016</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>P6 varón de 21 años, osteomielitis femoral, Riga</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eliava (14/15 menciones); Intesti (13/12 menciones); Pyo bacteriophage (4/12 menciones)</t>
+          <t>1 (EST-108 paciente 27 = paciente de EST-016)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el paciente 27 de EST-108 (infección ortopédica por P. aeruginosa, BFC 1 local, efecto aditivo con ceftazidima-avibactam) es el paciente de Riga de EST-016; EST-108 lo cita como ref. 21 (Racenis 2022). — EST-108: «27 Orthopaedic infection P. aeruginosa 14-1, PNM and ISP (BFC 1) Local» (p. 5) | EST-108: «21. Racenis, K. et al. Use of phage cocktail BFC 1.10 in combination with ceftazidime-avibactam» (p. 17) | EST-016: «In July 2018, a 21-year-old man was hospitalized after a road accident with open comminuted proximal right femoral and acetabular fractures» (p. 2)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1232,51 +1272,59 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-016: A | EST-108: A,B,C,D</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>P16 varón de 67 años, trasplante pulmonar (UCSD)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eliava (14/5 menciones); Pyo bacteriophage (4/30 menciones)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura del 2026-09-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el caso 2 de EST-034 (varón de 67 años, neumonía en trasplante pulmonar, AB-PA01 y luego cóctel de la Navy) es el receptor de trasplante pulmonar de EST-049 (AB-PA01, AB-PA01-m1 y cóctel de la Navy); EST-049 remite a la serie de 3 trasplantados de Aslam (EST-061). — EST-034: «2 67-year-old male [3] Pneumonia in lung transplant recipient Pseudomonas aeruginosa Episode 1: AB-PA01 (4 phages)» (p. 5) | EST-049: «The patient received AB-PA01 intravenously on days 1–14 and inhaled AB-PA01 on days 7–28» (p. 2) | EST-049: «Aslam S, Courtwright AM, Koval C, et al. Early clinical ex» (p. 5)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1286,51 +1334,59 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>EST-034: A | EST-049: A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EST-015</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>P16 varón de 67 años, trasplante pulmonar (UCSD)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PASA16 (51/6 menciones)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura del 2026-09-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el caso 2 de EST-034 (varón de 67 años, neumonía por P. aeruginosa tras trasplante pulmonar) es el paciente 1 de EST-061 (varón de 67 años, trasplante pulmonar bilateral por neumonitis por hipersensibilidad); mismo centro (UCSD, Aslam). — EST-034: «2 67-year-old male [3] Pneumonia in lung transplant recipient Pseudomonas aeruginosa» (p. 5) | EST-061: «Patient 1 was a 67‐year‐old man who underwent bilateral lung transplant for hypersensitivity pneumonitis» (p. 3)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1340,275 +1396,307 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-034: A | EST-061: A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EST-016</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
+          <t>P17 varón de 60 años, LVAD (UCSD); P18 varón de 82 años, LVAD (UCSD)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>identificador 10.3390/v11100891</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BFC-1 (26/12 menciones)</t>
+          <t>2 (EST-077 casos 1 y 2 = EST-034 casos 5 y 8)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>letonia</t>
+          <t>NO lo marco el detector: lo encontro la lectura del 2026-09-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>belgica</t>
+          <t>Solapan: los casos 1 y 2 de EST-077 (UCSD; varón de 60 años con LVAD de 2013 y varón de 82 años con LVAD de 2017, este último con fagos SDSU) son los casos 5 (60/M, infección de dispositivo, GD-1) y 8 (82/M, infección de VAD, SDSU1/SDSU2) de EST-034. — EST-034: «60-year-old male Ventricular assist device infection Pseudomonas aeruginosa GD-1 (3 phages)» (p. 5) | EST-034: «8 82-year-old male VAD infection Pseudomonas aeruginosa Episode 1: SDSU1 (2 phages: PAK_P, E217)» (p. 6) | EST-077: «This was a 60-year-old male with LVAD placement in 2013» (p. 5) | EST-077: «This was an 82-year-old male with an LVAD placed in 2017» (p. 9) | EST-077: «Initial two phage cocktail for 2 weeks: PAK_P1 and E217 (SDSU)» (p. 3)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>EST-034: A | EST-077: A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>gyofosteomyelitis:apopulation- (2019)11:891.doi:10.3390/v11100891 based study, 1969 to 2009. J Bone Joint Surg Am. (2015) 97:837– 10. TkhilaishviliT,WinklerT,MüllerM,PerkaC,TrampuzA.Bacteriophages 4</t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-046</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>P7 septicemia sensible solo a colistina</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Intesti (19/7 menciones)</t>
+          <t>1 (EST-108 paciente 13 = paciente de EST-046)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el paciente 13 de EST-108 (infección de herida y del torrente sanguíneo por P. aeruginosa, BFC 1 tópico e i.v., sin antibióticos concomitantes) es el paciente de EST-046 (varón de 61 años, Hospital Militar Reina Astrid, 2016); EST-108 lo cita como ref. 15 (Jennes 2017). — EST-108: «13 Wound and bloodstream infection Pseudomonas aeruginosa 14-1, PNM and ISP (BFC 1) Topical and intravenous» (p. 5) | EST-108: «15. Jennes, S. et al. Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury» (p. 17) | EST-046: «In June 2016, a 61-year-old man was hospitalised for Enterobacter cloacae peritonitis and severe abdominal sepsis» (p. 1)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-046: A | EST-108: A,B,C,D</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>P16 varón de 67 años, trasplante pulmonar (UCSD)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Eliava (14/15 menciones); Intesti (19/12 menciones)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>eeuu</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: EST-049 estudia la respuesta inmune del mismo receptor de trasplante pulmonar descrito como paciente 1 en EST-061, y lo cita como fuente clínica (ref. 2, Aslam 2019). — EST-049: «Aslam S, Courtwright AM, Koval C, et al. Early clinical ex» (p. 5) | EST-049: «The patient received AB-PA01 intravenously on days 1–14 and inhaled AB-PA01 on days 7–28» (p. 2) | EST-061: «Patient 1 was a 67‐year‐old man who underwent bilateral lung transplant for hypersensitivity pneumonitis» (p. 3)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-049: A | EST-061: A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>P8 niño pequeño, trasplante hepático, Bruselas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eliava (14/5 menciones)</t>
+          <t>1 (EST-108 paciente 20 = paciente de EST-062)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>firme: A declara casos ya publicados y cita a B</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el paciente 20 de EST-108 (trasplante hepático e infección del torrente sanguíneo por P. aeruginosa, BFC1) es el niño pequeño de EST-062; EST-108 lo cita como ref. 17 (Van Nieuwenhuyse 2022). — EST-108: «20 Liver transplant and bloodstream infection P» (p. 5) | EST-108: «17. Van Nieuwenhuyse, B. et al. Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantation in a toddler» (p. 17) | EST-108: «Twenty-seven of the 100 BT cases/patients were previously reported» (p. 2) | EST-062: «In September 2018, a male toddler suffering from biliary atresia was transferred from Algeria to the Saint-Luc University Hospital» (p. 2)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>EST-062: A | EST-108: A,B,C,D</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>P1 niña de 10 años, Berlin Heart EXCOR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Intesti (7/12 menciones)</t>
+          <t>1 (EST-070 caso 3 = EST-077 caso 3)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura del 2026-09-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el caso 3 de EST-070 (10/F, infección intravascular del Berlin heart, PASA16 + meropenem, fracaso) es el caso 3 de EST-077. — EST-070: «3 10 F P aeruginosa (MDR) Berlin heart intravascular infection Pa14NøPASA16 (APT) Meropenem» (p. 6) | EST-077: «A 10-year-old female with a genetic cardiomyopathy was admitted with cardiogenic shock and underwent placement of a Berlin Heart Excor VAD in January 2019 as a bridge to transplant.» (p. 11)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1618,51 +1706,59 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EST-070: A | EST-077: A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>P2 niña de 7 años, infección osteoarticular</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AB-PA01 (54/49 menciones)</t>
+          <t>1 (EST-070 caso 2 = paciente de EST-095)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>NO lo marco el detector: lo encontro la lectura del 2026-09-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>eeuu</t>
+          <t>Solapan: el caso 2 de EST-070 (7/F, osteomielitis por P. aeruginosa XDR, PASA16) es la paciente de EST-095. — EST-070: «2 7 F P aeruginosa (XDR) Osteomyelitis Pa14NøPASA16 (APT)» (p. 6) | EST-095: «complicating the internal fixation of a traumatic fracture-dislocation in a 7-yearold girl» (p. 1)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1672,25 +1768,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>EST-070: A | EST-095: A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1700,227 +1800,925 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
+          <t>P19 niño de 12 años, fascitis necrosante</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>identificador 10.1038/s41564-024-01705-x</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eliava (4/10 menciones); Intesti (19/3 menciones)</t>
+          <t>1 (EST-108 paciente 92 = paciente de EST-088; muy probable)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>alemania</t>
+          <t>NO lo marco el detector: lo encontro la lectura del 2026-09-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>multicentrico (europa)</t>
+          <t>Solapan (muy probable): el paciente 92 de EST-108 (fascitis necrosante generalizada con empiema y bacteriemia por S. aureus, P. aeruginosa y S. maltophilia, fagos ISP, 14-1, PNM, PT07 y BUCT700) coincide exactamente en infección, especies y fagos con el niño de 12 años de EST-088. EST-108 lo marcaba como no publicado porque EST-088 salió después. — EST-108: «92 Generalized necrotizing fasciitis, empyema, bacteremia S. aureus, P. aeruginosa and Stenotro-phomonas maltophilia ISP, 14-1, PNM, PT07 and BUCT700» (p. 6) | EST-088: «necrotizing fasciitis induced by Panton-Valentine Leukocidinproducing Methicillin-Resistant Staphylococcus aureus (MRSA) in a 12-year-old boy» (p. 1) | EST-088: «Multi-route phage therapy was initiated along with antibiotics against Staphylococcus aureus, Pseudomonas aeruginosa and Stenotrophomonas maltophilia» (p. 1) | EST-088: «aeruginosa phages PNM, 14-1 and PT07» (p. 3)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 (muy probable)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>EST-088: A | EST-108: A,B,C,D</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>, Geissberger F-D, Kufner V, Schmutz S, Böni J, et al. s41564-024-01705-x Optimization and validation of sample preparation for metagenomic sequencing of 7. Briot T, Kolenda C, Ferry T, Medina M, Laurent F, L</t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>P9 infección de la línea motriz de un LVAD (Racenis 2023)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BFC-1 (12/12 menciones)</t>
+          <t>1 (por cita; número de paciente en EST-108 no identificable)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>belgica</t>
+          <t>firme: A declara casos ya publicados y cita a B</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>belgica</t>
+          <t>Solapan (por cita): EST-108 incluye entre sus 27 casos ya publicados el de la ref. 25 (Racenis 2023, infección de la línea motriz de un LVAD), que es EST-124 (fagoterapia en junio de 2021, dentro de la ventana de EST-108). El número de paciente no se puede identificar en el PDF. — EST-108: «Twenty-seven of the 100 BT cases/patients were previously reported» (p. 2) | EST-108: «25. Racenis, K. et al. Successful bacteriophage–antibiotic combination therapy against multidrug-resistant Pseudomonas aeruginosa left ventricular assist device driveline infection» (p. 17) | EST-124: «On 16 June 2021, the operation began with extensive tissue debridement along the course of the driveline» (p. 4)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 (por cita)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>EST-108: A,B,C,D | EST-124: A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EST-003</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
+          <t>P10 osteomielitis pélvica, Lovaina (Onsea P1); P11 osteomielitis femoral, Lovaina (Onsea P2)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>identificador 10.1016/j.medj.2023.07.002</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PASA16 (23/51 menciones)</t>
+          <t>4 (2 con P. aeruginosa: EST-108 pacientes 22 y 24 = EST-164 pacientes 1 y 2)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>multicentrico (internacional)</t>
+          <t>NO lo marco el detector: lo encontro la lectura</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>israel</t>
+          <t>Solapan: los 4 pacientes de EST-164 (Lovaina) figuran en EST-108 con la ref. 19 (Onsea 2019). Los de P. aeruginosa son el paciente 22 (osteomielitis pélvica con P. aeruginosa y S. epidermidis = Onsea P1) y el 24 (osteomielitis femoral con P. aeruginosa y S. epidermidis = Onsea P2). Además, el 23 (fémur, S. aureus) y el 42 (fémur, E. faecalis, PyoPhage) son Onsea P3 y P4. — EST-108: «22 Chronic osteomyelitis of the pelvis P. aeruginosa and S. epidermidis 14-1, PNM, ISP (BFC 1)» (p. 5) | EST-108: «24 Chronic osteomyelitis of the femur P. aeruginosa and S. epidermidis 14-1, PNM, ISP (BFC 1)» (p. 5) | EST-108: «19. Onsea, J. et al. Bacteriophage application for difficult-to-treat musculoskeletal infections» (p. 17) | EST-164: «Three patients were treated for chronic osteomyelitis of the femur, and one for chronic osteomyelitis of the pelvis.» (p. 5)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>EST-108: A,B,C,D | EST-164: A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>dos veces, como dos estudios</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>SOLAPAMIENTO CONFIRMADO POR LECTURA</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>rapy related microbial succession associated j.medj.2023.07.002 with successful clinical outcome for a recurrent urinary tract infection. 20. Hope KD, Tunuguntla HP, Puri K, Spinner JA, Choudhry S,</t>
+          <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>EST-012</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EST-026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[DATO FALTANTE]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>firme: cita + marca de publicación previa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>EST-012 nombra NCT05269134 —el registro de EST-026— en su discusión: «These include a Phase 2 study for chronic salvage PJI (PhageBank, NCT05269134) and a phase 2 study for acute PJI cases (GLORIA, NCT06605651). These studies had challenges with enrollment…». Lo cita como ensayo que fracasó en reclutar, no como aquel en que se trató a su paciente.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EST-012: A | EST-026: —</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EST-012</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EST-015</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. Comparten el fago PASA16 (Adaptive Phage Therapeutics), pero EST-012 es un varón de 96 años con infección protésica de rodilla y cadera en Pittsburgh, y EST-015 un varón de 25 años con osteomielitis craneal tras electrocución en Johns Hopkins. Advertencia: ninguno de los dos es independiente, porque ambos pacientes están incluidos en EST-003 (serie PASA16 de Onallah 2023): EST-015 = caso 9 (cita 'Simner et al.') y EST-012 = caso 10 (misma aprobación UPMC EA21110067). Este par no está en la hoja. — EST-012: «A 96-year-old male with multiple comorbidities including heart failure presented with a chronic multidrug-resistant Pseudomonas aeruginosa infection in complex implants.» (p. 5) | EST-015: «We report the case of a 25-year-old male who experienced an accidental electrocution resulting in exposed calvarium in the left parieto-temporal region» (p. 1) | EST-003: «9 osteomyelitis 25/M debrided cranial bone and scalp tissue XDR i.v., 30 days BID» (p. 7) | EST-003: «10 prosthetic joint infection 96/M synovial fluid tissue sonicate S» (p. 7) | EST-003: «UPMC emergency approval number EA21110067» (p. 15) | EST-012: «We obtained compassionateuse IRB (EA21110067) from the University of Pittsburgh» (p. 13)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EST-012: A | EST-015: A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EST-016</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EST-164</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>a comprobar: cita + mismo producto</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. EST-016 es un varón de 21 años de Riga (Letonia) con osteomielitis femoral tras accidente de tráfico (jul-2018), tratado con BFC 1.10 local en dic-2018. EST-164 son 4 pacientes de Lovaina (Bélgica) con osteomielitis de pelvis y fémur; su P. aeruginosa XDR (paciente 2) procede de un politraumatismo por agresión en 2017. EST-016 cita a EST-164 solo como antecedente. Ambos pacientes (y los de EST-164) están además incluidos en EST-108 (refs. 19 y 21); ver los pares añadidos. — EST-016: «In July 2018, a 21-year-old man was hospitalized after a road accident with open comminuted proximal right femoral and acetabular fractures» (p. 2) | EST-164: «2017—Polytrauma after assault, with open segmental fractures of the right femur.» (p. 4) | EST-164: «Department of Trauma Surgery, University Hospitals Leuven, 3000 Leuven, Belgium» (p. 1)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EST-016: A | EST-164: A</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EST-038</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EST-044</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. EST-038 son adultos del EPTC (Tbilisi) tratados con Pyo/Intesti y fagos a medida; EST-044 es una niña de 2 años en la UCLA tratada con HC18 y HC20 i.v. EST-044 no usa Intesti (la señal viene de «intestinal»). — EST-038: «Patient #1 (43 years old, male with cystic fibrosis)» (p. 4) | EST-044: «A 2-year-old female patient with a history of biliary atresia underwent Kasai procedure at 4 months of age at a hospital in Mexico.» (p. 1)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EST-038: A | EST-044: A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EST-038</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>EST-080</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos, aunque ambos son del EPTC. EST-038 trata infecciones respiratorias (FQ 43 años, discinesia ciliar 64 años) y una ITU (72 años); EST-080 trata heridas quirúrgicas y osteomielitis de 60 a 74 años. Ni el sitio ni la edad ni el sexo coinciden. — EST-038: «Patient #1 (43 years old, male with cystic fibrosis)» (p. 4) | EST-038: «Patient #3 (72 years old, female with chronic bacterial cystitis)» (p. 7) | EST-080: «A 68-year-old male presented at the EPTC in December of 2017 with postsurgical infection.» (p. 5)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EST-038: A | EST-080: A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EST-038</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>EST-134</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Eliava (15/5 menciones); Pyo bacteriophage (12/30 menciones)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>eeuu</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>eeuu</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. EST-134 trata a varones operados de RTU de próstata en el TNCU (2016); EST-038 a 3 pacientes del EPTC (2017-2021), dos con infección respiratoria y una mujer con ITU por K. pneumoniae. — EST-038: «These cases were selected upon examination of EPTC clinical data from the years 2018 and 2019.» (p. 1) | EST-134: «From September 2016, 130 patients planned for TURP were screened in preparation for the RCT (Leitner et al., 2017) at the TNCU.» (p. 2)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EST-038: A | EST-134: A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EST-044</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EST-080</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. EST-044 es una niña de 2 años en la UCLA (EE. UU.) con fagos HC18/HC20; EST-080 son 4 adultos de 60 a 74 años del EPTC (Tbilisi) con productos Eliava. El «Intesti» de EST-044 es un falso positivo por «intestinal». — EST-044: «A 2-year-old female patient with a history of biliary atresia underwent Kasai procedure at 4 months of age at a hospital in Mexico.» (p. 1) | EST-080: «we conducted a retrospective analysis of four surgical patients who have sought treatment at the Eliava Phage Therapy Center, Tbilisi, Georgia» (p. 1)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EST-044: A | EST-080: A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EST-051</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EST-108</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0 (inferido por fechas; no verificable caso a caso)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>a comprobar: cita + mismo producto</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. EST-051 es un soldado ucraniano de 42 años herido en la guerra ruso-ucraniana (iniciada en feb-2022) y tratado en Ratisbona unos 8 meses después, es decir, fuera de la ventana de EST-108 (1-ene-2008 a 30-abr-2022). Además, EST-051 cita a EST-108 como trabajo externo recién publicado. Inferencia por fechas: EST-108 no lista sus pacientes (Supplementary Table 1 ausente). — EST-051: «A 42-year-old man suffered a war injury during the Russian war in Ukraine. He had a history of a gunshot and a blast injury to his proximal left femur 8 months ago.» (p. 2) | EST-051: «Pirnay et al. have just recently published clinical outcomes of their first 100 cases treated with personalized phage therapy.» (p. 2) | EST-108: «We reviewed the first 100 consecutive BT cases facilitated by a Belgian consortium between 1 January 2008 and 30 April 2022.» (p. 12)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0 (inferido por fechas)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>EST-051: A | EST-108: A,B,C,D</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EST-062</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EST-164</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. Ambos usan BFC1 de QAMH, pero EST-062 es un niño pequeño trasladado desde Argelia a Saint-Luc (Bruselas) por sepsis XDR tras trasplante hepático (sep-2018), y EST-164 son 4 adultos de Lovaina con osteomielitis de fémur o pelvis. Nota: EST-062 sí aparece en EST-108 (paciente 20), par que no está en esta hoja. Los dos están además incluidos en EST-108 (paciente 20 y pacientes 22-24, 42); ver los pares añadidos. — EST-062: «In September 2018, a male toddler suffering from biliary atresia was transferred from Algeria to the Saint-Luc University Hospital» (p. 2) | EST-164: «Three patients were treated for chronic osteomyelitis of the femur, and one for chronic osteomyelitis of the pelvis.» (p. 5)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EST-062: A | EST-164: A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EST-080</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EST-134</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No solapan: pacientes distintos. EST-080 trata heridas quirúrgicas en el EPTC (2016-2019); EST-134 trata ITU en varones operados de RTU de próstata en el TNCU con Pyo adaptado intravesical. El único caso con P. aeruginosa de cada artículo difiere (injerto cutáneo en un varón de 68 años frente a ITU post-RTU en uno de 56-60 años). — EST-080: «Bacterial culture of swabs taken from the infected area showed Pseudomonas aeruginosa.» (p. 5) | EST-080: «A 68-year-old male presented at the EPTC in December of 2017 with postsurgical infection.» (p. 5) | EST-134: «9 56–60 Pseudomonas 106 No data No data 60 1.3 Sudden fever and chills started on the 3rd day» (p. 5)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>EST-080: A | EST-134: A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EST-108</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EST-034</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>firme: A declara casos ya publicados y cita a B</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>EST-034 es una serie de un solo centro de Estados Unidos (Open Forum Infect Dis 2020) y EST-108 es el consorcio belga. EST-108 la cita en la discusión, no entre las referencias 6 y 13-26 de sus casos ya publicados.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>EST-108: A,B,C,D | EST-034: A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EST-108</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EST-044</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>firme: A declara casos ya publicados y cita a B</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>EST-044 se publicó en 2026 y EST-108 en 2024: un caso de 2026 no puede estar entre los «previously reported» de 2024. La cita va en el otro sentido.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EST-108: A,B,C,D | EST-044: A</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>una vez</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>DESCARTADO POR LECTURA</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -533,7 +533,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>31 filas de datos</t>
+          <t>30 filas de datos</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1981,32 +1981,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EST-026</t>
+          <t>EST-015</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[DATO FALTANTE]</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>firme: cita + marca de publicación previa</t>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>EST-012 nombra NCT05269134 —el registro de EST-026— en su discusión: «These include a Phase 2 study for chronic salvage PJI (PhageBank, NCT05269134) and a phase 2 study for acute PJI cases (GLORIA, NCT06605651). These studies had challenges with enrollment…». Lo cita como ensayo que fracasó en reclutar, no como aquel en que se trató a su paciente.</t>
+          <t>No solapan: pacientes distintos. Comparten el fago PASA16 (Adaptive Phage Therapeutics), pero EST-012 es un varón de 96 años con infección protésica de rodilla y cadera en Pittsburgh, y EST-015 un varón de 25 años con osteomielitis craneal tras electrocución en Johns Hopkins. Advertencia: ninguno de los dos es independiente, porque ambos pacientes están incluidos en EST-003 (serie PASA16 de Onallah 2023): EST-015 = caso 9 (cita 'Simner et al.') y EST-012 = caso 10 (misma aprobación UPMC EA21110067). Este par no está en la hoja. — EST-012: «A 96-year-old male with multiple comorbidities including heart failure presented with a chronic multidrug-resistant Pseudomonas aeruginosa infection in complex implants.» (p. 5) | EST-015: «We report the case of a 25-year-old male who experienced an accidental electrocution resulting in exposed calvarium in the left parieto-temporal region» (p. 1) | EST-003: «9 osteomyelitis 25/M debrided cranial bone and scalp tissue XDR i.v., 30 days BID» (p. 7) | EST-003: «10 prosthetic joint infection 96/M synovial fluid tissue sonicate S» (p. 7) | EST-003: «UPMC emergency approval number EA21110067» (p. 15) | EST-012: «We obtained compassionateuse IRB (EA21110067) from the University of Pittsburgh» (p. 13)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EST-012: A | EST-026: —</t>
+          <t>EST-012: A | EST-015: A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2038,12 +2038,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-016</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EST-015</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+          <t>a comprobar: cita + mismo producto</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos. Comparten el fago PASA16 (Adaptive Phage Therapeutics), pero EST-012 es un varón de 96 años con infección protésica de rodilla y cadera en Pittsburgh, y EST-015 un varón de 25 años con osteomielitis craneal tras electrocución en Johns Hopkins. Advertencia: ninguno de los dos es independiente, porque ambos pacientes están incluidos en EST-003 (serie PASA16 de Onallah 2023): EST-015 = caso 9 (cita 'Simner et al.') y EST-012 = caso 10 (misma aprobación UPMC EA21110067). Este par no está en la hoja. — EST-012: «A 96-year-old male with multiple comorbidities including heart failure presented with a chronic multidrug-resistant Pseudomonas aeruginosa infection in complex implants.» (p. 5) | EST-015: «We report the case of a 25-year-old male who experienced an accidental electrocution resulting in exposed calvarium in the left parieto-temporal region» (p. 1) | EST-003: «9 osteomyelitis 25/M debrided cranial bone and scalp tissue XDR i.v., 30 days BID» (p. 7) | EST-003: «10 prosthetic joint infection 96/M synovial fluid tissue sonicate S» (p. 7) | EST-003: «UPMC emergency approval number EA21110067» (p. 15) | EST-012: «We obtained compassionateuse IRB (EA21110067) from the University of Pittsburgh» (p. 13)</t>
+          <t>No solapan: pacientes distintos. EST-016 es un varón de 21 años de Riga (Letonia) con osteomielitis femoral tras accidente de tráfico (jul-2018), tratado con BFC 1.10 local en dic-2018. EST-164 son 4 pacientes de Lovaina (Bélgica) con osteomielitis de pelvis y fémur; su P. aeruginosa XDR (paciente 2) procede de un politraumatismo por agresión en 2017. EST-016 cita a EST-164 solo como antecedente. Ambos pacientes (y los de EST-164) están además incluidos en EST-108 (refs. 19 y 21); ver los pares añadidos. — EST-016: «In July 2018, a 21-year-old man was hospitalized after a road accident with open comminuted proximal right femoral and acetabular fractures» (p. 2) | EST-164: «2017—Polytrauma after assault, with open segmental fractures of the right femur.» (p. 4) | EST-164: «Department of Trauma Surgery, University Hospitals Leuven, 3000 Leuven, Belgium» (p. 1)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EST-012: A | EST-015: A</t>
+          <t>EST-016: A | EST-164: A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EST-016</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos. EST-016 es un varón de 21 años de Riga (Letonia) con osteomielitis femoral tras accidente de tráfico (jul-2018), tratado con BFC 1.10 local en dic-2018. EST-164 son 4 pacientes de Lovaina (Bélgica) con osteomielitis de pelvis y fémur; su P. aeruginosa XDR (paciente 2) procede de un politraumatismo por agresión en 2017. EST-016 cita a EST-164 solo como antecedente. Ambos pacientes (y los de EST-164) están además incluidos en EST-108 (refs. 19 y 21); ver los pares añadidos. — EST-016: «In July 2018, a 21-year-old man was hospitalized after a road accident with open comminuted proximal right femoral and acetabular fractures» (p. 2) | EST-164: «2017—Polytrauma after assault, with open segmental fractures of the right femur.» (p. 4) | EST-164: «Department of Trauma Surgery, University Hospitals Leuven, 3000 Leuven, Belgium» (p. 1)</t>
+          <t>No solapan: pacientes distintos. EST-038 son adultos del EPTC (Tbilisi) tratados con Pyo/Intesti y fagos a medida; EST-044 es una niña de 2 años en la UCLA tratada con HC18 y HC20 i.v. EST-044 no usa Intesti (la señal viene de «intestinal»). — EST-038: «Patient #1 (43 years old, male with cystic fibrosis)» (p. 4) | EST-044: «A 2-year-old female patient with a history of biliary atresia underwent Kasai procedure at 4 months of age at a hospital in Mexico.» (p. 1)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EST-016: A | EST-164: A</t>
+          <t>EST-038: A | EST-044: A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos. EST-038 son adultos del EPTC (Tbilisi) tratados con Pyo/Intesti y fagos a medida; EST-044 es una niña de 2 años en la UCLA tratada con HC18 y HC20 i.v. EST-044 no usa Intesti (la señal viene de «intestinal»). — EST-038: «Patient #1 (43 years old, male with cystic fibrosis)» (p. 4) | EST-044: «A 2-year-old female patient with a history of biliary atresia underwent Kasai procedure at 4 months of age at a hospital in Mexico.» (p. 1)</t>
+          <t>No solapan: pacientes distintos, aunque ambos son del EPTC. EST-038 trata infecciones respiratorias (FQ 43 años, discinesia ciliar 64 años) y una ITU (72 años); EST-080 trata heridas quirúrgicas y osteomielitis de 60 a 74 años. Ni el sitio ni la edad ni el sexo coinciden. — EST-038: «Patient #1 (43 years old, male with cystic fibrosis)» (p. 4) | EST-038: «Patient #3 (72 years old, female with chronic bacterial cystitis)» (p. 7) | EST-080: «A 68-year-old male presented at the EPTC in December of 2017 with postsurgical infection.» (p. 5)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>EST-038: A | EST-044: A</t>
+          <t>EST-038: A | EST-080: A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos, aunque ambos son del EPTC. EST-038 trata infecciones respiratorias (FQ 43 años, discinesia ciliar 64 años) y una ITU (72 años); EST-080 trata heridas quirúrgicas y osteomielitis de 60 a 74 años. Ni el sitio ni la edad ni el sexo coinciden. — EST-038: «Patient #1 (43 years old, male with cystic fibrosis)» (p. 4) | EST-038: «Patient #3 (72 years old, female with chronic bacterial cystitis)» (p. 7) | EST-080: «A 68-year-old male presented at the EPTC in December of 2017 with postsurgical infection.» (p. 5)</t>
+          <t>No solapan: pacientes distintos. EST-134 trata a varones operados de RTU de próstata en el TNCU (2016); EST-038 a 3 pacientes del EPTC (2017-2021), dos con infección respiratoria y una mujer con ITU por K. pneumoniae. — EST-038: «These cases were selected upon examination of EPTC clinical data from the years 2018 and 2019.» (p. 1) | EST-134: «From September 2016, 130 patients planned for TURP were screened in preparation for the RCT (Leitner et al., 2017) at the TNCU.» (p. 2)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EST-038: A | EST-080: A</t>
+          <t>EST-038: A | EST-134: A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2286,12 +2286,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos. EST-134 trata a varones operados de RTU de próstata en el TNCU (2016); EST-038 a 3 pacientes del EPTC (2017-2021), dos con infección respiratoria y una mujer con ITU por K. pneumoniae. — EST-038: «These cases were selected upon examination of EPTC clinical data from the years 2018 and 2019.» (p. 1) | EST-134: «From September 2016, 130 patients planned for TURP were screened in preparation for the RCT (Leitner et al., 2017) at the TNCU.» (p. 2)</t>
+          <t>No solapan: pacientes distintos. EST-044 es una niña de 2 años en la UCLA (EE. UU.) con fagos HC18/HC20; EST-080 son 4 adultos de 60 a 74 años del EPTC (Tbilisi) con productos Eliava. El «Intesti» de EST-044 es un falso positivo por «intestinal». — EST-044: «A 2-year-old female patient with a history of biliary atresia underwent Kasai procedure at 4 months of age at a hospital in Mexico.» (p. 1) | EST-080: «we conducted a retrospective analysis of four surgical patients who have sought treatment at the Eliava Phage Therapy Center, Tbilisi, Georgia» (p. 1)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EST-038: A | EST-134: A</t>
+          <t>EST-044: A | EST-080: A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2348,12 +2348,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2368,27 +2368,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 (inferido por fechas; no verificable caso a caso)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
+          <t>a comprobar: cita + mismo producto</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos. EST-044 es una niña de 2 años en la UCLA (EE. UU.) con fagos HC18/HC20; EST-080 son 4 adultos de 60 a 74 años del EPTC (Tbilisi) con productos Eliava. El «Intesti» de EST-044 es un falso positivo por «intestinal». — EST-044: «A 2-year-old female patient with a history of biliary atresia underwent Kasai procedure at 4 months of age at a hospital in Mexico.» (p. 1) | EST-080: «we conducted a retrospective analysis of four surgical patients who have sought treatment at the Eliava Phage Therapy Center, Tbilisi, Georgia» (p. 1)</t>
+          <t>No solapan: pacientes distintos. EST-051 es un soldado ucraniano de 42 años herido en la guerra ruso-ucraniana (iniciada en feb-2022) y tratado en Ratisbona unos 8 meses después, es decir, fuera de la ventana de EST-108 (1-ene-2008 a 30-abr-2022). Además, EST-051 cita a EST-108 como trabajo externo recién publicado. Inferencia por fechas: EST-108 no lista sus pacientes (Supplementary Table 1 ausente). — EST-051: «A 42-year-old man suffered a war injury during the Russian war in Ukraine. He had a history of a gunshot and a blast injury to his proximal left femur 8 months ago.» (p. 2) | EST-051: «Pirnay et al. have just recently published clinical outcomes of their first 100 cases treated with personalized phage therapy.» (p. 2) | EST-108: «We reviewed the first 100 consecutive BT cases facilitated by a Belgian consortium between 1 January 2008 and 30 April 2022.» (p. 12)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 (inferido por fechas)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EST-044: A | EST-080: A</t>
+          <t>EST-051: A | EST-108: A,B,C,D</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2410,12 +2410,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0 (inferido por fechas; no verificable caso a caso)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>a comprobar: cita + mismo producto</t>
+          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos. EST-051 es un soldado ucraniano de 42 años herido en la guerra ruso-ucraniana (iniciada en feb-2022) y tratado en Ratisbona unos 8 meses después, es decir, fuera de la ventana de EST-108 (1-ene-2008 a 30-abr-2022). Además, EST-051 cita a EST-108 como trabajo externo recién publicado. Inferencia por fechas: EST-108 no lista sus pacientes (Supplementary Table 1 ausente). — EST-051: «A 42-year-old man suffered a war injury during the Russian war in Ukraine. He had a history of a gunshot and a blast injury to his proximal left femur 8 months ago.» (p. 2) | EST-051: «Pirnay et al. have just recently published clinical outcomes of their first 100 cases treated with personalized phage therapy.» (p. 2) | EST-108: «We reviewed the first 100 consecutive BT cases facilitated by a Belgian consortium between 1 January 2008 and 30 April 2022.» (p. 12)</t>
+          <t>No solapan: pacientes distintos. Ambos usan BFC1 de QAMH, pero EST-062 es un niño pequeño trasladado desde Argelia a Saint-Luc (Bruselas) por sepsis XDR tras trasplante hepático (sep-2018), y EST-164 son 4 adultos de Lovaina con osteomielitis de fémur o pelvis. Nota: EST-062 sí aparece en EST-108 (paciente 20), par que no está en esta hoja. Los dos están además incluidos en EST-108 (paciente 20 y pacientes 22-24, 42); ver los pares añadidos. — EST-062: «In September 2018, a male toddler suffering from biliary atresia was transferred from Algeria to the Saint-Luc University Hospital» (p. 2) | EST-164: «Three patients were treated for chronic osteomyelitis of the femur, and one for chronic osteomyelitis of the pelvis.» (p. 5)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0 (inferido por fechas)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EST-051: A | EST-108: A,B,C,D</t>
+          <t>EST-062: A | EST-164: A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2472,12 +2472,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No solapan: pacientes distintos. Ambos usan BFC1 de QAMH, pero EST-062 es un niño pequeño trasladado desde Argelia a Saint-Luc (Bruselas) por sepsis XDR tras trasplante hepático (sep-2018), y EST-164 son 4 adultos de Lovaina con osteomielitis de fémur o pelvis. Nota: EST-062 sí aparece en EST-108 (paciente 20), par que no está en esta hoja. Los dos están además incluidos en EST-108 (paciente 20 y pacientes 22-24, 42); ver los pares añadidos. — EST-062: «In September 2018, a male toddler suffering from biliary atresia was transferred from Algeria to the Saint-Luc University Hospital» (p. 2) | EST-164: «Three patients were treated for chronic osteomyelitis of the femur, and one for chronic osteomyelitis of the pelvis.» (p. 5)</t>
+          <t>No solapan: pacientes distintos. EST-080 trata heridas quirúrgicas en el EPTC (2016-2019); EST-134 trata ITU en varones operados de RTU de próstata en el TNCU con Pyo adaptado intravesical. El único caso con P. aeruginosa de cada artículo difiere (injerto cutáneo en un varón de 68 años frente a ITU post-RTU en uno de 56-60 años). — EST-080: «Bacterial culture of swabs taken from the infected area showed Pseudomonas aeruginosa.» (p. 5) | EST-080: «A 68-year-old male presented at the EPTC in December of 2017 with postsurgical infection.» (p. 5) | EST-134: «9 56–60 Pseudomonas 106 No data No data 60 1.3 Sudden fever and chills started on the 3rd day» (p. 5)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>EST-062: A | EST-164: A</t>
+          <t>EST-080: A | EST-134: A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>firme: A declara casos ya publicados y cita a B</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>EST-034 es una serie de un solo centro de Estados Unidos (Open Forum Infect Dis 2020) y EST-108 es el consorcio belga. EST-108 la cita en la discusión, no entre las referencias 6 y 13-26 de sus casos ya publicados.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>a comprobar: mismo producto y país, sin cita entre ellos</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No solapan: pacientes distintos. EST-080 trata heridas quirúrgicas en el EPTC (2016-2019); EST-134 trata ITU en varones operados de RTU de próstata en el TNCU con Pyo adaptado intravesical. El único caso con P. aeruginosa de cada artículo difiere (injerto cutáneo en un varón de 68 años frente a ITU post-RTU en uno de 56-60 años). — EST-080: «Bacterial culture of swabs taken from the infected area showed Pseudomonas aeruginosa.» (p. 5) | EST-080: «A 68-year-old male presented at the EPTC in December of 2017 with postsurgical infection.» (p. 5) | EST-134: «9 56–60 Pseudomonas 106 No data No data 60 1.3 Sudden fever and chills started on the 3rd day» (p. 5)</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EST-080: A | EST-134: A</t>
+          <t>EST-108: A,B,C,D | EST-034: A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EST-034</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EST-034 es una serie de un solo centro de Estados Unidos (Open Forum Infect Dis 2020) y EST-108 es el consorcio belga. EST-108 la cita en la discusión, no entre las referencias 6 y 13-26 de sus casos ya publicados.</t>
+          <t>EST-044 se publicó en 2026 y EST-108 en 2024: un caso de 2026 no puede estar entre los «previously reported» de 2024. La cita va en el otro sentido.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EST-108: A,B,C,D | EST-034: A</t>
+          <t>EST-108: A,B,C,D | EST-044: A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2655,70 +2655,8 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>EST-108</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>EST-044</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ninguno</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ninguno</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>firme: A declara casos ya publicados y cita a B</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>EST-044 se publicó en 2026 y EST-108 en 2024: un caso de 2026 no puede estar entre los «previously reported» de 2024. La cita va en el otro sentido.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>EST-108: A,B,C,D | EST-044: A</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>una vez</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>DESCARTADO POR LECTURA</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Ninguna.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L32"/>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -516,192 +523,199 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sección 4.4, limitación séptima. Un paciente que sale en tres pares tiene la misma clave en los tres y se cuenta una vez.</t>
+          <t>Sección 4.4, en la limitación sobre pacientes descritos en más de un estudio. Un paciente que sale en tres pares tiene la misma clave en los tres y se cuenta una vez.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>30 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>estudio_1</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: estudio_1</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>estudio_2</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: estudio_2</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>clave_del_paciente</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: clave_del_paciente</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>pacientes_de_esa_clave</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: pacientes_de_esa_clave</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>paciente_o_identificador</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: paciente_o_identificador</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>senal_que_lo_marco</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: senal_que_lo_marco</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: evidencia</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>pacientes_potencialmente_duplicados</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: pacientes_potencialmente_duplicados</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>brazos_afectados</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: brazos_afectados</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>se_conto_una_o_dos_veces</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: se_conto_una_o_dos_veces</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: veredicto</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>accion_necesaria</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: accion_necesaria</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -734,62 +748,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>estudio_1</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>estudio_2</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>clave_del_paciente</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>pacientes_de_esa_clave</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>paciente_o_identificador</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>senal_que_lo_marco</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>pacientes_potencialmente_duplicados</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>brazos_afectados</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>se_conto_una_o_dos_veces</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>accion_necesaria</t>
         </is>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -715,7 +715,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -715,7 +715,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$N$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Cada par de estudios que podía describir a los mismos pacientes, con el veredicto tras leer los dos artículos y los pacientes que comparten, una clave por persona.</t>
+          <t>Cada par de estudios que podía describir a los mismos pacientes, con el veredicto tras leer los dos artículos y los pacientes que comparten, una clave por persona. En «Señal que lo marcó», «NO lo marco el detector» quiere decir que el par lo encontró una lectura, y la etiqueta dice cuál: la del modelo de lenguaje o la relectura de los autores, con su fecha. Quién firmó cada veredicto y cuándo está en «Firmado por» y «Fecha»: 28, «DANNY VALDIVIEZO/ NATALY TRELLES»; 2, «sin firma: descarte de la lectura del modelo del 2026-09-22».</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>estudio_1</t>
+          <t>Estudio 1</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>estudio_2</t>
+          <t>Estudio 2</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>clave_del_paciente</t>
+          <t>Clave del paciente</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>pacientes_de_esa_clave</t>
+          <t>Pacientes con esa clave</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>paciente_o_identificador</t>
+          <t>Paciente o identificador</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>senal_que_lo_marco</t>
+          <t>Señal que lo marcó</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>pacientes_potencialmente_duplicados</t>
+          <t>Pacientes posiblemente duplicados</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>brazos_afectados</t>
+          <t>Brazos afectados</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>se_conto_una_o_dos_veces</t>
+          <t>¿Se contó una o dos veces?</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>veredicto</t>
+          <t>Veredicto</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>accion_necesaria</t>
+          <t>Acción necesaria</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -705,15 +705,39 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Firmado por</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>columna interna: firmado_por</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>columna interna: fecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Generado el 2026-10-19</t>
         </is>
@@ -730,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -738,44 +762,46 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>estudio_1</t>
+          <t>Estudio 1</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>estudio_2</t>
+          <t>Estudio 2</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>clave_del_paciente</t>
+          <t>Clave del paciente</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>pacientes_de_esa_clave</t>
+          <t>Pacientes con esa clave</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>paciente_o_identificador</t>
+          <t>Paciente o identificador</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>senal_que_lo_marco</t>
+          <t>Señal que lo marcó</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
@@ -785,27 +811,37 @@
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>pacientes_potencialmente_duplicados</t>
+          <t>Pacientes posiblemente duplicados</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>brazos_afectados</t>
+          <t>Brazos afectados</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>se_conto_una_o_dos_veces</t>
+          <t>¿Se contó una o dos veces?</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>veredicto</t>
+          <t>Veredicto</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>accion_necesaria</t>
+          <t>Acción necesaria</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Firmado por</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Fecha</t>
         </is>
       </c>
     </row>
@@ -870,6 +906,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -932,6 +978,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -961,7 +1017,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -992,6 +1048,16 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1089,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1054,6 +1120,16 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1116,6 +1192,16 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1233,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1178,6 +1264,16 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1305,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1240,6 +1336,16 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1377,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1302,6 +1408,16 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1366,6 +1482,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1428,6 +1554,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1490,6 +1626,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1519,7 +1665,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1550,6 +1696,16 @@
       <c r="L13" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1614,6 +1770,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1676,6 +1842,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1738,6 +1914,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1800,6 +1986,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1862,6 +2058,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1924,6 +2130,16 @@
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1953,7 +2169,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NO lo marco el detector: lo encontro la lectura</t>
+          <t>NO lo marco el detector: lo encontro la lectura del modelo, 2026-09-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1984,6 +2200,16 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Declararlo. Lectura firmada por los dos autores el 2026-09-30.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -2048,6 +2274,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2110,6 +2346,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2172,6 +2418,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2234,6 +2490,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2296,6 +2562,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2358,6 +2634,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2420,6 +2706,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2482,6 +2778,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2544,6 +2850,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>DANNY VALDIVIEZO/ NATALY TRELLES</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2606,6 +2922,16 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>sin firma: descarte de la lectura del modelo del 2026-09-22</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2668,9 +2994,19 @@
           <t>Ninguna.</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>sin firma: descarte de la lectura del modelo del 2026-09-22</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:N31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
+++ b/verificables revisión sistemática/S21_solapamiento_de_pacientes.xlsx
@@ -739,7 +739,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
